--- a/artfynd/A 37012-2025 artfynd.xlsx
+++ b/artfynd/A 37012-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128808179</v>
       </c>
       <c r="B2" t="n">
-        <v>91010</v>
+        <v>91037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128808085</v>
       </c>
       <c r="B3" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2025 artfynd.xlsx
+++ b/artfynd/A 37012-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128808179</v>
       </c>
       <c r="B2" t="n">
-        <v>91037</v>
+        <v>91042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128808085</v>
       </c>
       <c r="B3" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2025 artfynd.xlsx
+++ b/artfynd/A 37012-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128808179</v>
       </c>
       <c r="B2" t="n">
-        <v>91042</v>
+        <v>91047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128808085</v>
       </c>
       <c r="B3" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2025 artfynd.xlsx
+++ b/artfynd/A 37012-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128808179</v>
       </c>
       <c r="B2" t="n">
-        <v>91047</v>
+        <v>91051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128808085</v>
       </c>
       <c r="B3" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2025 artfynd.xlsx
+++ b/artfynd/A 37012-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128808179</v>
       </c>
       <c r="B2" t="n">
-        <v>91051</v>
+        <v>91056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128808085</v>
       </c>
       <c r="B3" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2025 artfynd.xlsx
+++ b/artfynd/A 37012-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128808179</v>
       </c>
       <c r="B2" t="n">
-        <v>91063</v>
+        <v>91066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128808085</v>
       </c>
       <c r="B3" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2025 artfynd.xlsx
+++ b/artfynd/A 37012-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128808179</v>
       </c>
       <c r="B2" t="n">
-        <v>91066</v>
+        <v>91069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128808085</v>
       </c>
       <c r="B3" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2025 artfynd.xlsx
+++ b/artfynd/A 37012-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128808179</v>
       </c>
       <c r="B2" t="n">
-        <v>91069</v>
+        <v>91073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128808085</v>
       </c>
       <c r="B3" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2025 artfynd.xlsx
+++ b/artfynd/A 37012-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128808179</v>
       </c>
       <c r="B2" t="n">
-        <v>91073</v>
+        <v>91080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128808085</v>
       </c>
       <c r="B3" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2025 artfynd.xlsx
+++ b/artfynd/A 37012-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128808179</v>
+        <v>128808085</v>
       </c>
       <c r="B2" t="n">
-        <v>91080</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5754</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knapergruvorna, Knapergruvorna, Gstr</t>
+          <t>Söderåsens naturreservat, Söderåsens naturreservat, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576294</v>
+        <v>576287</v>
       </c>
       <c r="R2" t="n">
-        <v>6708614</v>
+        <v>6708621</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,131 +779,15 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stephen Hinton</t>
+          <t>Maj-Lis Koivisto</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stephen Hinton</t>
+          <t>Maj-Lis Koivisto</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>128808085</v>
-      </c>
-      <c r="B3" t="n">
-        <v>92871</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Söderåsens naturreservat, Söderåsens naturreservat, Gstr</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>576287</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6708621</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Hofors</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Gästrikland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Torsåker</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Maj-Lis Koivisto</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Maj-Lis Koivisto</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37012-2025 artfynd.xlsx
+++ b/artfynd/A 37012-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128808085</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2025 artfynd.xlsx
+++ b/artfynd/A 37012-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128808085</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2025 artfynd.xlsx
+++ b/artfynd/A 37012-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128808085</v>
       </c>
       <c r="B2" t="n">
-        <v>92860</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2025 artfynd.xlsx
+++ b/artfynd/A 37012-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,8 +793,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128808085</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>